--- a/backend/src/data/ot_procedures_v2.xlsx
+++ b/backend/src/data/ot_procedures_v2.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="83">
   <si>
     <t>Procedure ID</t>
   </si>
@@ -44,6 +44,222 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>OT-C1</t>
+  </si>
+  <si>
+    <t>OP002002</t>
+  </si>
+  <si>
+    <t>Scenario C Patient</t>
+  </si>
+  <si>
+    <t>Arthroscopy</t>
+  </si>
+  <si>
+    <t>Dr. Patel</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>Successful</t>
+  </si>
+  <si>
+    <t>COMPLETED</t>
+  </si>
+  <si>
+    <t>OT-685598</t>
+  </si>
+  <si>
+    <t>OP001050</t>
+  </si>
+  <si>
+    <t>Ravi Nair</t>
+  </si>
+  <si>
+    <t>Dr. Reddy</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>Routine</t>
+  </si>
+  <si>
+    <t>SCHEDULED</t>
+  </si>
+  <si>
+    <t>OT-FD7793</t>
+  </si>
+  <si>
+    <t>OP001051</t>
+  </si>
+  <si>
+    <t>Priya Reddy</t>
+  </si>
+  <si>
+    <t>Fracture Fixation</t>
+  </si>
+  <si>
+    <t>OT-360943</t>
+  </si>
+  <si>
+    <t>OP001052</t>
+  </si>
+  <si>
+    <t>Ramesh Iyer</t>
+  </si>
+  <si>
+    <t>Spinal Fusion</t>
+  </si>
+  <si>
+    <t>Dr. Sharma</t>
+  </si>
+  <si>
+    <t>OT-0A6F05</t>
+  </si>
+  <si>
+    <t>OP001053</t>
+  </si>
+  <si>
+    <t>Arjun Iyer</t>
+  </si>
+  <si>
+    <t>Carpal Tunnel Release</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>OT-E94503</t>
+  </si>
+  <si>
+    <t>OP001054</t>
+  </si>
+  <si>
+    <t>Krishna Naidu</t>
+  </si>
+  <si>
+    <t>OT-91342D</t>
+  </si>
+  <si>
+    <t>OP001055</t>
+  </si>
+  <si>
+    <t>Sunita Singh</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>OT-B2BA6A</t>
+  </si>
+  <si>
+    <t>OP001056</t>
+  </si>
+  <si>
+    <t>Krishna Iyer</t>
+  </si>
+  <si>
+    <t>TKR (Total Knee Replacement)</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>OT-66F5FD</t>
+  </si>
+  <si>
+    <t>OP001057</t>
+  </si>
+  <si>
+    <t>Priya Sharma</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>OT-FA229F</t>
+  </si>
+  <si>
+    <t>OP001058</t>
+  </si>
+  <si>
+    <t>Ravi Kumar</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>OT-BDDAC5</t>
+  </si>
+  <si>
+    <t>OP001059</t>
+  </si>
+  <si>
+    <t>Saanvi Sharma</t>
+  </si>
+  <si>
+    <t>OT-547427</t>
+  </si>
+  <si>
+    <t>OP001060</t>
+  </si>
+  <si>
+    <t>Kavya Naidu</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>OT-21224D</t>
+  </si>
+  <si>
+    <t>OP001061</t>
+  </si>
+  <si>
+    <t>Suresh Nair</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>OT-539E4C</t>
+  </si>
+  <si>
+    <t>OP001062</t>
+  </si>
+  <si>
+    <t>Ramesh Singh</t>
+  </si>
+  <si>
+    <t>OT-79BF80</t>
+  </si>
+  <si>
+    <t>OP001063</t>
+  </si>
+  <si>
+    <t>Arjun Gowda</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>OT-CE875C</t>
+  </si>
+  <si>
+    <t>OP001064</t>
+  </si>
+  <si>
+    <t>Ananya Gowda</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
   </si>
 </sst>
 </file>
@@ -420,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -468,6 +684,566 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2">
+        <v>25000</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3">
+        <v>25606</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4">
+        <v>40780</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5">
+        <v>49595</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6">
+        <v>62</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6">
+        <v>21041</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7">
+        <v>61</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <v>25096</v>
+      </c>
+      <c r="J7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8">
+        <v>59</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8">
+        <v>25107</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9">
+        <v>33473</v>
+      </c>
+      <c r="J9" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10">
+        <v>77</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10">
+        <v>46276</v>
+      </c>
+      <c r="J10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11">
+        <v>82</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11">
+        <v>29584</v>
+      </c>
+      <c r="J11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12">
+        <v>35851</v>
+      </c>
+      <c r="J12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13">
+        <v>46983</v>
+      </c>
+      <c r="J13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14">
+        <v>29032</v>
+      </c>
+      <c r="J14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15">
+        <v>30906</v>
+      </c>
+      <c r="J15" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16">
+        <v>61</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16">
+        <v>38143</v>
+      </c>
+      <c r="J16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17">
+        <v>81</v>
+      </c>
+      <c r="E17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17">
+        <v>46612</v>
+      </c>
+      <c r="J17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
